--- a/resources/tool_obs_health_facility_iphra_v2.xlsx
+++ b/resources/tool_obs_health_facility_iphra_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E4A25A-7CAF-4137-9A4A-4FF934E32DE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4019D88A-1AB7-4BD0-AAD8-F261EC006331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{27C29DD6-0256-4DF1-82F8-B613F9F4F125}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{27C29DD6-0256-4DF1-82F8-B613F9F4F125}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="359">
   <si>
     <t>type</t>
   </si>
@@ -161,9 +161,6 @@
   </si>
   <si>
     <t>Other, specify</t>
-  </si>
-  <si>
-    <t>Borehole</t>
   </si>
   <si>
     <t>source</t>
@@ -275,24 +272,15 @@
     <t>If yes, what is the source?</t>
   </si>
   <si>
-    <t>Is there a water supply within the health facility compound?</t>
-  </si>
-  <si>
     <t xml:space="preserve">If no, how far away is the nearest water supply? </t>
   </si>
   <si>
-    <t>What is the primary water source in the facility?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Is there water storage capacity at this facility? </t>
   </si>
   <si>
     <t>If yes, what is the water storage capacity (litres)?</t>
   </si>
   <si>
-    <t>select_one storage</t>
-  </si>
-  <si>
     <t>water_available</t>
   </si>
   <si>
@@ -302,24 +290,6 @@
     <t>meters</t>
   </si>
   <si>
-    <t>primary_storage</t>
-  </si>
-  <si>
-    <t>storage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protected hand dug well    </t>
-  </si>
-  <si>
-    <t>Unprotected hand dug well</t>
-  </si>
-  <si>
-    <t>protected_handdug</t>
-  </si>
-  <si>
-    <t>unprotected_handdug</t>
-  </si>
-  <si>
     <t>water_capacity</t>
   </si>
   <si>
@@ -446,15 +416,9 @@
     <t>Are there handwashing facilities with soap and water available at the toilets / latrines?</t>
   </si>
   <si>
-    <t>Is there a demarcated, fenced off waste area?</t>
-  </si>
-  <si>
     <t>Is there a pit for organic waste?</t>
   </si>
   <si>
-    <t>Is there a functioning incinerator?</t>
-  </si>
-  <si>
     <t>Is there a pit for sharps?</t>
   </si>
   <si>
@@ -470,45 +434,9 @@
     <t>none</t>
   </si>
   <si>
-    <t>flush_pour</t>
-  </si>
-  <si>
-    <t>pit_latrine_wo_slab</t>
-  </si>
-  <si>
-    <t>pit_latrine_with_slab</t>
-  </si>
-  <si>
-    <t>open_hole</t>
-  </si>
-  <si>
-    <t>hanging_latrine</t>
-  </si>
-  <si>
-    <t>dedicated_open_defecation</t>
-  </si>
-  <si>
     <t>None</t>
   </si>
   <si>
-    <t>Flush or pour / flush toilet</t>
-  </si>
-  <si>
-    <t>Pit latrine without slab</t>
-  </si>
-  <si>
-    <t>Pit latrine with slab</t>
-  </si>
-  <si>
-    <t>Open hole</t>
-  </si>
-  <si>
-    <t>Haning latrine /Toilet</t>
-  </si>
-  <si>
-    <t>Dedicated open defecation point</t>
-  </si>
-  <si>
     <t>latrine_groups</t>
   </si>
   <si>
@@ -728,9 +656,6 @@
     <t>Are sharps bins available in all areas where patients are treated?</t>
   </si>
   <si>
-    <t>fenced_waste</t>
-  </si>
-  <si>
     <t>separate_refuse</t>
   </si>
   <si>
@@ -759,12 +684,6 @@
   </si>
   <si>
     <t>Please specify observer name</t>
-  </si>
-  <si>
-    <t>primary_storage_other</t>
-  </si>
-  <si>
-    <t>selected(${primary_storage}, 'other')</t>
   </si>
   <si>
     <t>selected(${water_capacity}, 'yes')</t>
@@ -792,13 +711,424 @@
   </si>
   <si>
     <t>comments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is the primary water supply for this health facility? </t>
+  </si>
+  <si>
+    <t>select_one water_source</t>
+  </si>
+  <si>
+    <t>water_source</t>
+  </si>
+  <si>
+    <t>Public taps or standpipes</t>
+  </si>
+  <si>
+    <t>Borehole / tubewell</t>
+  </si>
+  <si>
+    <t>Protected well</t>
+  </si>
+  <si>
+    <t>Protected spring</t>
+  </si>
+  <si>
+    <t>Rainwater</t>
+  </si>
+  <si>
+    <t>Tap water in the dwelling, yard, plot, or piped into a neighbours home</t>
+  </si>
+  <si>
+    <t>Packaged water (bottle or sachet)</t>
+  </si>
+  <si>
+    <t>Delivered water (tanker trucks, small carts, tanks, drums)</t>
+  </si>
+  <si>
+    <t>Water kiosks</t>
+  </si>
+  <si>
+    <t>Unprotected well</t>
+  </si>
+  <si>
+    <t>Unprotected spring</t>
+  </si>
+  <si>
+    <t>Surface water</t>
+  </si>
+  <si>
+    <t>surface_water</t>
+  </si>
+  <si>
+    <t>tap_water_premisis</t>
+  </si>
+  <si>
+    <t>public_tap</t>
+  </si>
+  <si>
+    <t>protected_well</t>
+  </si>
+  <si>
+    <t>protected_spring</t>
+  </si>
+  <si>
+    <t>unprotected_well</t>
+  </si>
+  <si>
+    <t>unprotected_spring</t>
+  </si>
+  <si>
+    <t>rainwater</t>
+  </si>
+  <si>
+    <t>packaged_waater</t>
+  </si>
+  <si>
+    <t>deliverd_water</t>
+  </si>
+  <si>
+    <t>water_kiosk</t>
+  </si>
+  <si>
+    <t>Is the main water supply within the health facility compound?</t>
+  </si>
+  <si>
+    <t>water_source_other</t>
+  </si>
+  <si>
+    <t>Please describe other</t>
+  </si>
+  <si>
+    <t>selected(${water_source}, 'other')</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Flush and pour-flush toilets connected to sewers</t>
+  </si>
+  <si>
+    <t>Flush and pour-flush toilets connected to septic tanks or pits</t>
+  </si>
+  <si>
+    <t>Ventilated improved pit latrine (VIP)</t>
+  </si>
+  <si>
+    <t>Pit latrines with slabs</t>
+  </si>
+  <si>
+    <t>Composting toilets, including twin pit latrines with slabs and container based systems</t>
+  </si>
+  <si>
+    <t>Flush and pour-flush toilets or latrines flushed to open drain or elsewhere</t>
+  </si>
+  <si>
+    <t>Pit latrines without slabs, or slabs constructed from materials that are not durable and easy to clean</t>
+  </si>
+  <si>
+    <t>Open pits</t>
+  </si>
+  <si>
+    <t>Hanging toilets / latrines</t>
+  </si>
+  <si>
+    <t>Bucket latrines</t>
+  </si>
+  <si>
+    <t>Open defecation into bush, field, or ditch</t>
+  </si>
+  <si>
+    <t>Open defecation into surface water, including beached, rivers, streams, drainage channels, seas, or oceans</t>
+  </si>
+  <si>
+    <t>flush_network</t>
+  </si>
+  <si>
+    <t>flush_tank</t>
+  </si>
+  <si>
+    <t>vip</t>
+  </si>
+  <si>
+    <t>pit_latrine_slab</t>
+  </si>
+  <si>
+    <t>composting</t>
+  </si>
+  <si>
+    <t>flush_open_drain</t>
+  </si>
+  <si>
+    <t>open_pit</t>
+  </si>
+  <si>
+    <t>hanging</t>
+  </si>
+  <si>
+    <t>bucket</t>
+  </si>
+  <si>
+    <t>open_defecation_field</t>
+  </si>
+  <si>
+    <t>open_defecation_water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the handwashing facility within 5 meters of the latrines? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the handwashing facility within 5 meters of point of medical care? </t>
+  </si>
+  <si>
+    <t>soap_water_latrines_distance</t>
+  </si>
+  <si>
+    <t>soap_water_care_distance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How is health care waste disposed of? </t>
+  </si>
+  <si>
+    <t>select_one health_waste_method</t>
+  </si>
+  <si>
+    <t>health_waste_method</t>
+  </si>
+  <si>
+    <t>Autoclave</t>
+  </si>
+  <si>
+    <t>2-chamber industrial incinerator</t>
+  </si>
+  <si>
+    <t>1 chamber incinerator (drum/brick/de Monfort)</t>
+  </si>
+  <si>
+    <t>Remove offsite (stored in covered container)</t>
+  </si>
+  <si>
+    <t>Remove offsite (stored in other protected environment)</t>
+  </si>
+  <si>
+    <t>Open burning (flat ground, no protection)</t>
+  </si>
+  <si>
+    <t>Open burning (pit or protected ground)</t>
+  </si>
+  <si>
+    <t>Dump without burning (flat ground, no protection)</t>
+  </si>
+  <si>
+    <t>Dump without burning (covered pit or pit latrine, no protection)</t>
+  </si>
+  <si>
+    <t>Dump without burning (open pit, no protection)</t>
+  </si>
+  <si>
+    <t>Remove offsite (stored unprotected)</t>
+  </si>
+  <si>
+    <t>autoclave</t>
+  </si>
+  <si>
+    <t>industrial_incinerator</t>
+  </si>
+  <si>
+    <t>simple_incinerator</t>
+  </si>
+  <si>
+    <t>dump_protected</t>
+  </si>
+  <si>
+    <t>dump_open</t>
+  </si>
+  <si>
+    <t>Dump without burning (protected ground or pit)</t>
+  </si>
+  <si>
+    <t>remove_offsite_covered</t>
+  </si>
+  <si>
+    <t>open_burning_protected</t>
+  </si>
+  <si>
+    <t>remove_offsite_other</t>
+  </si>
+  <si>
+    <t>open_burning_unprotected</t>
+  </si>
+  <si>
+    <t>dump_unprotected</t>
+  </si>
+  <si>
+    <t>dump_covered</t>
+  </si>
+  <si>
+    <t>remove_offsite_unprotected</t>
+  </si>
+  <si>
+    <t>waste_method</t>
+  </si>
+  <si>
+    <t>waste_method_other</t>
+  </si>
+  <si>
+    <t>Is the incinerator functioning?</t>
+  </si>
+  <si>
+    <t>label::French (fr)</t>
+  </si>
+  <si>
+    <t>yes_no_dnk</t>
+  </si>
+  <si>
+    <t>Oui</t>
+  </si>
+  <si>
+    <t>Non</t>
+  </si>
+  <si>
+    <t>dont_know</t>
+  </si>
+  <si>
+    <t>Don't know</t>
+  </si>
+  <si>
+    <t>Ne sait pas</t>
+  </si>
+  <si>
+    <t>yes_no_dnk_pnta</t>
+  </si>
+  <si>
+    <t>prefer_not_to_answer</t>
+  </si>
+  <si>
+    <t>Decline to answer</t>
+  </si>
+  <si>
+    <t>Préfère ne pas répondre</t>
+  </si>
+  <si>
+    <t>yes_no_other</t>
+  </si>
+  <si>
+    <t>Autre</t>
+  </si>
+  <si>
+    <t>sex</t>
+  </si>
+  <si>
+    <t>male</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Homme</t>
+  </si>
+  <si>
+    <t>female</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Femme</t>
+  </si>
+  <si>
+    <t>enum_id</t>
+  </si>
+  <si>
+    <t>Team 1</t>
+  </si>
+  <si>
+    <t>Équipe 1</t>
+  </si>
+  <si>
+    <t>Team 2</t>
+  </si>
+  <si>
+    <t>Équipe 2</t>
+  </si>
+  <si>
+    <t>Team 3</t>
+  </si>
+  <si>
+    <t>Équipe 3</t>
+  </si>
+  <si>
+    <t>Team 4</t>
+  </si>
+  <si>
+    <t>Équipe 4</t>
+  </si>
+  <si>
+    <t>Team 5</t>
+  </si>
+  <si>
+    <t>Équipe 5</t>
+  </si>
+  <si>
+    <t>admin1</t>
+  </si>
+  <si>
+    <t>admin1a</t>
+  </si>
+  <si>
+    <t>To be updated by country</t>
+  </si>
+  <si>
+    <t>À mettre à jour par le pays</t>
+  </si>
+  <si>
+    <t>admin1b</t>
+  </si>
+  <si>
+    <t>admin1c</t>
+  </si>
+  <si>
+    <t>admin2</t>
+  </si>
+  <si>
+    <t>admin2a</t>
+  </si>
+  <si>
+    <t>admin2b</t>
+  </si>
+  <si>
+    <t>admin2c</t>
+  </si>
+  <si>
+    <t>admin3</t>
+  </si>
+  <si>
+    <t>admin3a</t>
+  </si>
+  <si>
+    <t>admin3b</t>
+  </si>
+  <si>
+    <t>admin3c</t>
+  </si>
+  <si>
+    <t>admin4</t>
+  </si>
+  <si>
+    <t>admin4a</t>
+  </si>
+  <si>
+    <t>admin4b</t>
+  </si>
+  <si>
+    <t>admin4c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -819,8 +1149,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -845,6 +1181,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -858,7 +1200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -871,11 +1213,66 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1236,7 +1633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D2A72A4-B69F-42B0-BA64-020C51FE6931}">
-  <dimension ref="A1:O141"/>
+  <dimension ref="A1:M144"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.85546875" style="2" customWidth="1"/>
@@ -1252,7 +1649,7 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>246</v>
+        <v>219</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1288,7 +1685,7 @@
         <v>10</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -1372,10 +1769,10 @@
         <v>19</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>237</v>
+        <v>212</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="F7" s="2" t="b">
         <v>1</v>
@@ -1392,7 +1789,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F8" s="2" t="b">
         <v>1</v>
@@ -1409,7 +1806,7 @@
         <v>23</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>24</v>
@@ -1433,17 +1830,17 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>53101</v>
+      <c r="A11" s="8">
+        <v>14229</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>24</v>
@@ -1456,17 +1853,17 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>51104</v>
+      <c r="A12" s="8">
+        <v>14205</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>24</v>
@@ -1476,17 +1873,17 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>51104</v>
+      <c r="A13" s="8">
+        <v>14205</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>24</v>
@@ -1496,17 +1893,17 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>51105</v>
+      <c r="A14" s="8">
+        <v>14206</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>24</v>
@@ -1516,106 +1913,97 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>51105</v>
+      <c r="A15" s="8">
+        <v>14206</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F15" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>51105</v>
+      <c r="A16" s="8">
+        <v>14206</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="F16" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>44201</v>
+      <c r="A17" s="8">
+        <v>14501</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F17" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="8">
+        <v>14501</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="8">
+        <v>14501</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>44201</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F18" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>44202</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="C19" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>79</v>
+        <v>248</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>24</v>
@@ -1623,42 +2011,45 @@
       <c r="F19" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="H19" s="2" t="s">
-        <v>26</v>
-      </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>44202</v>
+      <c r="A20" s="8">
+        <v>14501</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>239</v>
+        <v>85</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>45</v>
+        <v>76</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="F20" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>240</v>
+        <v>80</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>44202</v>
+      <c r="A21" s="8">
+        <v>14502</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>24</v>
@@ -1668,66 +2059,66 @@
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>44202</v>
+      <c r="A22" s="8">
+        <v>14502</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F22" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>44203</v>
+      <c r="A23" s="8">
+        <v>14503</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F23" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>44203</v>
+      <c r="A24" s="8">
+        <v>14503</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>24</v>
@@ -1737,17 +2128,17 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>44203</v>
+      <c r="A25" s="8">
+        <v>14503</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>24</v>
@@ -1756,27 +2147,27 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>242</v>
+        <v>215</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>44203</v>
+      <c r="A26" s="8">
+        <v>14503</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="F26" s="2" t="b">
         <v>1</v>
@@ -1785,94 +2176,94 @@
         <v>26</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>44203</v>
+      <c r="A27" s="8">
+        <v>14503</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F27" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>44203</v>
+      <c r="A28" s="8">
+        <v>14503</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>244</v>
+        <v>217</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="F28" s="7" t="b">
         <v>1</v>
       </c>
       <c r="G28" s="7"/>
       <c r="H28" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>245</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>44203</v>
+      <c r="A29" s="8">
+        <v>14503</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>44203</v>
+      <c r="A30" s="8">
+        <v>14503</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>24</v>
@@ -1882,43 +2273,43 @@
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>44203</v>
+      <c r="A31" s="8">
+        <v>14503</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F31" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>44203</v>
+      <c r="A32" s="8">
+        <v>14503</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>24</v>
@@ -1928,131 +2319,131 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>44203</v>
+      <c r="A33" s="8">
+        <v>14503</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F33" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F33" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>44203</v>
+      <c r="A34" s="8">
+        <v>14503</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>244</v>
+        <v>217</v>
       </c>
       <c r="C34" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E34" s="7" t="s">
         <v>117</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>127</v>
       </c>
       <c r="F34" s="7" t="b">
         <v>1</v>
       </c>
       <c r="G34" s="7"/>
       <c r="H34" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>44203</v>
+      <c r="A35" s="8">
+        <v>14503</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>244</v>
+        <v>217</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F35" s="7" t="b">
         <v>1</v>
       </c>
       <c r="G35" s="7"/>
       <c r="H35" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>53301</v>
+      <c r="A36" s="8">
+        <v>14505</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F36" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>53301</v>
+      <c r="A37" s="8">
+        <v>14505</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F37" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>53301</v>
+      <c r="A38" s="8">
+        <v>14505</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>24</v>
@@ -2062,69 +2453,69 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>53301</v>
+      <c r="A39" s="8">
+        <v>14505</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F39" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H39" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F39" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>53301</v>
+      <c r="A40" s="8">
+        <v>14505</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F40" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H40" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F40" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>53301</v>
+      <c r="A41" s="8">
+        <v>14505</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>24</v>
@@ -2134,43 +2525,43 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>53301</v>
+      <c r="A42" s="8">
+        <v>14505</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F42" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H42" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F42" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>53301</v>
+      <c r="A43" s="8">
+        <v>14505</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>24</v>
@@ -2180,63 +2571,63 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>53301</v>
+      <c r="A44" s="8">
+        <v>14505</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F44" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H44" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F44" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>53301</v>
+      <c r="A45" s="8">
+        <v>14505</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="F45" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>53301</v>
+      <c r="A46" s="8">
+        <v>14505</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>24</v>
@@ -2246,17 +2637,17 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>53301</v>
+      <c r="A47" s="8">
+        <v>14505</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>24</v>
@@ -2265,41 +2656,41 @@
         <v>1</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>53301</v>
+      <c r="A48" s="8">
+        <v>14505</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>45</v>
+        <v>250</v>
       </c>
       <c r="F48" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>53301</v>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="8">
+        <v>14506</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>24</v>
@@ -2308,38 +2699,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>53301</v>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="8">
+        <v>14506</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C50" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F50" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="8">
+        <v>14506</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="D50" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="F50" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>53401</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>235</v>
-      </c>
       <c r="C51" s="2" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>24</v>
@@ -2348,38 +2739,35 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>53401</v>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="8">
+        <v>14506</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>235</v>
+        <v>22</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>223</v>
+        <v>278</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>24</v>
+        <v>276</v>
       </c>
       <c r="F52" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>53201</v>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="8">
+        <v>14506</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>228</v>
+        <v>199</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>24</v>
@@ -2387,82 +2775,70 @@
       <c r="F53" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="O53" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>53201</v>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="8">
+        <v>14506</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>229</v>
+        <v>279</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>24</v>
+        <v>277</v>
       </c>
       <c r="F54" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>53201</v>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="8">
+        <v>14504</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>22</v>
+        <v>281</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>230</v>
+        <v>307</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>24</v>
+        <v>280</v>
       </c>
       <c r="F55" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>53201</v>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="8">
+        <v>14504</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>231</v>
+        <v>308</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="F56" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>53201</v>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="8">
+        <v>14504</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>136</v>
+        <v>200</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>24</v>
@@ -2471,18 +2847,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>53201</v>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="8">
+        <v>14504</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>24</v>
@@ -2491,75 +2867,135 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>53201</v>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="8">
+        <v>14504</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>234</v>
+        <v>206</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="E59" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F59" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="8">
+        <v>14504</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F59" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="3">
+      <c r="F60" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="8">
+        <v>14504</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F61" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="8">
+        <v>14504</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F62" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="3">
         <v>10000</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B63" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
+      <c r="C63" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
         <v>10000</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B64" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C64" s="2" t="s">
+        <v>221</v>
+      </c>
       <c r="D64" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="67" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D67" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="140" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C140" s="2" t="s">
+    <row r="143" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C143" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="141" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="D141" s="2" t="s">
+    <row r="144" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D144" s="2" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C7:C8">
-    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C23:C28">
-    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C34:C35">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2567,7 +3003,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D63B81B-C0DE-4D5C-B8D8-1821B93262B2}">
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.85546875" style="2" customWidth="1"/>
@@ -2577,9 +3013,9 @@
     <col min="5" max="16384" width="8.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>246</v>
+        <v>219</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>27</v>
@@ -2590,9 +3026,12 @@
       <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+      <c r="E1" s="5" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="9">
         <v>10000</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -2605,8 +3044,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="9">
         <v>10000</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -2619,514 +3058,1386 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>51105</v>
-      </c>
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B6" t="s">
+        <v>311</v>
+      </c>
+      <c r="C6" t="s">
+        <v>314</v>
+      </c>
+      <c r="D6" t="s">
+        <v>315</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B7" t="s">
+        <v>317</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B8" t="s">
+        <v>317</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B9" t="s">
+        <v>317</v>
+      </c>
+      <c r="C9" t="s">
+        <v>314</v>
+      </c>
+      <c r="D9" t="s">
+        <v>315</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B10" t="s">
+        <v>317</v>
+      </c>
+      <c r="C10" t="s">
+        <v>318</v>
+      </c>
+      <c r="D10" t="s">
+        <v>319</v>
+      </c>
+      <c r="E10" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B11" t="s">
+        <v>321</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B12" t="s">
+        <v>321</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B13" t="s">
+        <v>321</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E13" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="C16" s="9">
+        <v>1</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="C17" s="9">
+        <v>2</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="C18" s="9">
+        <v>3</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="C19" s="9">
+        <v>4</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="C20" s="9">
+        <v>5</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="8">
+        <v>14206</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="8">
+        <v>14206</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="8">
+        <v>14206</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>51105</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>51105</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>53101</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="2" t="s">
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="8">
+        <v>14501</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="8">
+        <v>14501</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="8">
+        <v>14501</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="8">
+        <v>14501</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="8">
+        <v>14501</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="8">
+        <v>14501</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="8">
+        <v>14501</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="8">
+        <v>14501</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="8">
+        <v>14501</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="8">
+        <v>14501</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="8">
+        <v>14501</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="8">
+        <v>14501</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="8">
+        <v>14501</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="8">
+        <v>14229</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="8">
+        <v>14229</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D50" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>53101</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="J50" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="8">
+        <v>14229</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="8">
+        <v>14229</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>53101</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="D52" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>53101</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>44202</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>44202</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>44202</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>44202</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" s="2" t="s">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="8">
+        <v>14503</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="8">
+        <v>14503</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="8">
+        <v>14505</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="8">
+        <v>14505</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="8">
+        <v>14505</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="8">
+        <v>14505</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="8">
+        <v>14505</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="8">
+        <v>14505</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="8">
+        <v>14505</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="8">
+        <v>14505</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="8">
+        <v>14505</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="8">
+        <v>14505</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="8">
+        <v>14505</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="8">
+        <v>14505</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="8">
+        <v>14505</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="8">
+        <v>14505</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="8">
+        <v>14505</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="8">
+        <v>14505</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="8">
+        <v>14505</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="8">
+        <v>14505</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="8">
+        <v>14505</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="8">
+        <v>14505</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D74" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>44203</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>44203</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>53301</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>53301</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>53301</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>53301</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>53301</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>53301</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>53301</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>53301</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>53301</v>
-      </c>
-      <c r="B25" s="2" t="s">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="8">
+        <v>14506</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="8">
+        <v>14506</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>53301</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="D76" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>53301</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C27" s="2" t="s">
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="8">
+        <v>14506</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D77" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>53301</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C28" s="2" t="s">
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="8">
+        <v>14506</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="8">
+        <v>14506</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="8">
+        <v>14506</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D80" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>53301</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C29" s="2" t="s">
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="8">
+        <v>14506</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="8">
+        <v>14506</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D82" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>53301</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>53301</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>53301</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>53301</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>53301</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>53401</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>53401</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>53401</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>53401</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>53401</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>215</v>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="8">
+        <v>14504</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="8">
+        <v>14504</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="8">
+        <v>14504</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="8">
+        <v>14504</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="8">
+        <v>14504</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="8">
+        <v>14504</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="8">
+        <v>14504</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="8">
+        <v>14504</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="8">
+        <v>14504</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="8">
+        <v>14504</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="8">
+        <v>14504</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="8">
+        <v>14504</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>293</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="C4:C6">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7:C10">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C11:C12">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:C20">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C21:C32">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3136,7 +4447,10 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="8.7109375" style="2"/>
+    <col min="1" max="1" width="35.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -3152,7 +4466,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -3167,6 +4481,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DE51FB2AFBB2DD429D3D11FE759FFC43" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1354c8e90e28409d311bbba5db8dc335">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4877444-78fa-4cfa-bafc-d6c64fafc061" xmlns:ns3="d0fa6634-326e-4532-91a2-52bea7ac9212" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dbb4473bd7833dc3543803a005841490" ns2:_="" ns3:_="">
     <xsd:import namespace="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
@@ -3407,7 +4730,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
@@ -3418,16 +4741,15 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0EC5A08-1E92-4958-B309-E39C6B5C0D09}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60670709-FEBC-4BB6-B6F4-017E9C3B19CF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3446,7 +4768,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E77C68E-7FCA-4366-8842-EC37F1748509}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -3457,12 +4779,4 @@
     <ds:schemaRef ds:uri="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0EC5A08-1E92-4958-B309-E39C6B5C0D09}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>